--- a/public/3-brigada.xlsx
+++ b/public/3-brigada.xlsx
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="174">
-        <f>+'4-5 бетлар'!X6</f>
+        <f>+'4-5 бетлар'!Y6</f>
         <v>0</v>
       </c>
       <c r="AA8" s="142"/>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="174">
-        <f>+'4-5 бетлар'!X30</f>
+        <f>+'4-5 бетлар'!Y30</f>
         <v>0</v>
       </c>
       <c r="AA10" s="142"/>
